--- a/Generators/Experiment with utility data leak/utility results/12. Air Quality/TRTR_TSTR_results_merged.xlsx
+++ b/Generators/Experiment with utility data leak/utility results/12. Air Quality/TRTR_TSTR_results_merged.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Quality_Metrics" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="TRTR_Results" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="All_Comparisons" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Summary" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="CTGAN" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="CopulaGAN" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="TVAE" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="GaussianCopula" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="WGAN_GP" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="CTABGAN" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quality_Metrics" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TRTR_Results" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All_Comparisons" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CTGAN" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CopulaGAN" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TVAE" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GaussianCopula" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WGAN_GP" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CTABGAN" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TabDDPM" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ForestDiffusion" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,13 +28,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -43,7 +48,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -51,12 +56,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -422,18 +436,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Quality Score</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Generator</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Quality_Score</t>
         </is>
       </c>
     </row>
@@ -446,55 +470,31 @@
       <c r="B2" t="n">
         <v>0.8178852680962627</v>
       </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>WGAN_GP</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0.9248901750895357</v>
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.4839480616728481</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CTGAN</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0.7137047098302216</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CopulaGAN</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0.6877142646533299</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>TVAE</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.9200152254785867</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>GaussianCopula</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.9487675622153033</v>
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.9515441371692741</v>
       </c>
     </row>
   </sheetData>
@@ -512,152 +512,152 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>R2 Mean_TRTR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>R2 Std_TRTR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>MSE Mean_TRTR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>MSE Std_TRTR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>RMSE Mean_TRTR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RMSE Std_TRTR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>MAE Mean_TRTR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MAE Std_TRTR</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>R2 (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>MSE (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>RMSE (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>MAE (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>R2 Mean_TSTR</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>R2 Std_TSTR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>MSE Mean_TSTR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>MSE Std_TSTR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>RMSE Mean_TSTR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>RMSE Std_TSTR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>MAE Mean_TSTR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>MAE Std_TSTR</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>R2 (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>MSE (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>RMSE (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>MAE (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>R2_Drop</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>MSE_Increase</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>RMSE_Increase</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>MAE_Increase</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
@@ -1780,6 +1780,2578 @@
       <c r="AD11" t="inlineStr">
         <is>
           <t>CTABGAN</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AD11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>R2 Mean_TRTR</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>R2 Std_TRTR</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>MSE Mean_TRTR</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>MSE Std_TRTR</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE Mean_TRTR</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE Std_TRTR</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>MAE Mean_TRTR</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>MAE Std_TRTR</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>R2 (Mean±Std)_TRTR</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>MSE (Mean±Std)_TRTR</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE (Mean±Std)_TRTR</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>MAE (Mean±Std)_TRTR</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>R2 Mean_TSTR</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>R2 Std_TSTR</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>MSE Mean_TSTR</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>MSE Std_TSTR</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE Mean_TSTR</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE Std_TSTR</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>MAE Mean_TSTR</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>MAE Std_TSTR</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>R2 (Mean±Std)_TSTR</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>MSE (Mean±Std)_TSTR</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE (Mean±Std)_TSTR</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>MAE (Mean±Std)_TSTR</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>R2_Drop</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>MSE_Increase</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_Increase</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>MAE_Increase</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Synthetic_Model</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ExtraTrees</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.9116048161286496</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.001626983670777651</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4571.288966849999</v>
+      </c>
+      <c r="E2" t="n">
+        <v>84.13820954652159</v>
+      </c>
+      <c r="F2" t="n">
+        <v>67.6084497138725</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6216865261302376</v>
+      </c>
+      <c r="H2" t="n">
+        <v>48.363375</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.4247965326188557</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.9116 ± 0.0016</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>4571.2890 ± 84.1382</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>67.6084 ± 0.6217</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>48.3634 ± 0.4248</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>-0.2476985211651928</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.1063491796695852</v>
+      </c>
+      <c r="P2" t="n">
+        <v>64523.76966666502</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>5499.766054728349</v>
+      </c>
+      <c r="R2" t="n">
+        <v>253.772829810411</v>
+      </c>
+      <c r="S2" t="n">
+        <v>11.09596848775243</v>
+      </c>
+      <c r="T2" t="n">
+        <v>200.6349508907648</v>
+      </c>
+      <c r="U2" t="n">
+        <v>11.36178203789082</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>-0.2477 ± 0.1063</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>64523.7697 ± 5499.7661</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>253.7728 ± 11.0960</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>200.6350 ± 11.3618</t>
+        </is>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.159303337293842</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>59952.48069981502</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>186.1643800965385</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>152.2715758907648</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GradientBoost</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.9102206965008903</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.0001952188595595897</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4642.867649149999</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10.0955932183435</v>
+      </c>
+      <c r="F3" t="n">
+        <v>68.13855121779409</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.0740748948746275</v>
+      </c>
+      <c r="H3" t="n">
+        <v>50.13660360458156</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.09856557051916351</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.9102 ± 0.0002</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>4642.8676 ± 10.0956</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>68.1386 ± 0.0741</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>50.1366 ± 0.0986</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>0.1580785346976827</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.657001166779273e-16</v>
+      </c>
+      <c r="P3" t="n">
+        <v>43539.32122469468</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.9387389466973e-11</v>
+      </c>
+      <c r="R3" t="n">
+        <v>208.6607802743359</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4.403072291788041e-14</v>
+      </c>
+      <c r="T3" t="n">
+        <v>162.3152754450487</v>
+      </c>
+      <c r="U3" t="n">
+        <v>4.493866839778178e-14</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.1581 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>43539.3212 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>208.6608 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>162.3153 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.7521421618032076</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>38896.45357554468</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>140.5222290565418</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>112.1786718404672</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.9028473645236117</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.002042436733120966</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5024.173843</v>
+      </c>
+      <c r="E4" t="n">
+        <v>105.6230452237469</v>
+      </c>
+      <c r="F4" t="n">
+        <v>70.87748756684246</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7453852776203633</v>
+      </c>
+      <c r="H4" t="n">
+        <v>51.09162</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.5291182723172551</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.9028 ± 0.0020</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>5024.1738 ± 105.6230</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>70.8775 ± 0.7454</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>51.0916 ± 0.5291</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>-0.2937394689168336</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.06936555461018579</v>
+      </c>
+      <c r="P4" t="n">
+        <v>66904.74187875641</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3587.186321490817</v>
+      </c>
+      <c r="R4" t="n">
+        <v>258.5645689784054</v>
+      </c>
+      <c r="S4" t="n">
+        <v>7.007535070753652</v>
+      </c>
+      <c r="T4" t="n">
+        <v>194.6835479481866</v>
+      </c>
+      <c r="U4" t="n">
+        <v>7.007873836343863</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>-0.2937 ± 0.0694</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>66904.7419 ± 3587.1863</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>258.5646 ± 7.0075</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>194.6835 ± 7.0079</t>
+        </is>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.196586833440445</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>61880.56803575641</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>187.687081411563</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>143.5919279481866</v>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>LinearRegression</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.8851906599789372</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1.110223024625157e-16</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5937.276742287724</v>
+      </c>
+      <c r="E5" t="n">
+        <v>9.094947017729282e-13</v>
+      </c>
+      <c r="F5" t="n">
+        <v>77.05372633615926</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.4210854715202e-14</v>
+      </c>
+      <c r="H5" t="n">
+        <v>59.38520770130062</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.8852 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>5937.2767 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>77.0537 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>59.3852 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>-0.1550190367355349</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>59730.92139064085</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>7.275957614183426e-12</v>
+      </c>
+      <c r="R5" t="n">
+        <v>244.3991026796965</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>193.990499676167</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>-0.1550 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>59730.9214 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>244.3991 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>193.9905 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.040209696714472</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>53793.64464835313</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>167.3453763435373</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>134.6052919748664</v>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.8851906081365704</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1.110223024625157e-16</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5937.279423275867</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>77.05374373303265</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>59.38491809936655</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.8852 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>5937.2794 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>77.0537 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>59.3849 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.1550127975995497</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>59730.59873852064</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>244.3984425861193</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.842170943040401e-14</v>
+      </c>
+      <c r="T6" t="n">
+        <v>193.9900329807481</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>-0.1550 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>59730.5987 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>244.3984 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>193.9900 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.04020340573612</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>53793.31931524477</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>167.3446988530866</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>134.6051148813815</v>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.8851866436459515</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5937.484443859918</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>77.05507409548002</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>59.37304037963372</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.8852 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>5937.4844 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>77.0551 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>59.3730 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>-0.1546172572629998</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>59710.14367414693</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>7.275957614183426e-12</v>
+      </c>
+      <c r="R7" t="n">
+        <v>244.3565912230462</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.842170943040401e-14</v>
+      </c>
+      <c r="T7" t="n">
+        <v>193.9600260389704</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>-0.1546 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>59710.1437 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>244.3566 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>193.9600 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.039803900908951</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>53772.65923028701</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>167.3015171275662</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>134.5869856593367</v>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.8851727350548286</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5938.203715955524</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>77.05974121391482</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.4210854715202e-14</v>
+      </c>
+      <c r="H8" t="n">
+        <v>59.35659563760858</v>
+      </c>
+      <c r="I8" t="n">
+        <v>7.105427357601002e-15</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.8852 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>5938.2037 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>77.0597 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>59.3566 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>-0.1542229437520715</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>59689.75205411694</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>7.275957614183426e-12</v>
+      </c>
+      <c r="R8" t="n">
+        <v>244.3148625321778</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.842170943040401e-14</v>
+      </c>
+      <c r="T8" t="n">
+        <v>193.9300943300856</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>-0.1542 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>59689.7521 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>244.3149 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>193.9301 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.0393956788069</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>53751.54833816141</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>167.2551213182629</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>134.5734986924771</v>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.8823432762978853</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.110223024625157e-16</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6084.527</v>
+      </c>
+      <c r="E9" t="n">
+        <v>9.094947017729282e-13</v>
+      </c>
+      <c r="F9" t="n">
+        <v>78.00337813197578</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.4210854715202e-14</v>
+      </c>
+      <c r="H9" t="n">
+        <v>54.43299999999999</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.8823 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>6084.5270 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>78.0034 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>54.4330 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>-5.168602711759162</v>
+      </c>
+      <c r="O9" t="n">
+        <v>8.881784197001252e-16</v>
+      </c>
+      <c r="P9" t="n">
+        <v>319004.5461999999</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>5.820766091346741e-11</v>
+      </c>
+      <c r="R9" t="n">
+        <v>564.8048744478041</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.13686837721616e-13</v>
+      </c>
+      <c r="T9" t="n">
+        <v>492.295</v>
+      </c>
+      <c r="U9" t="n">
+        <v>5.684341886080801e-14</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>-5.1686 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>319004.5462 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>564.8049 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>492.2950 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Z9" t="n">
+        <v>6.050945988057047</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>312920.0191999999</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>486.8014963158283</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>437.862</v>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.790261804743337</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.01019794917541283</v>
+      </c>
+      <c r="D10" t="n">
+        <v>10846.4495</v>
+      </c>
+      <c r="E10" t="n">
+        <v>527.3791004033532</v>
+      </c>
+      <c r="F10" t="n">
+        <v>104.1152993360513</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.54046140778499</v>
+      </c>
+      <c r="H10" t="n">
+        <v>74.37949999999998</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.635971347548608</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.7903 ± 0.0102</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>10846.4495 ± 527.3791</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>104.1153 ± 2.5405</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>74.3795 ± 1.6360</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>-3.62274256602067</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.1150740718166244</v>
+      </c>
+      <c r="P10" t="n">
+        <v>239061.577375</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>5950.967143542908</v>
+      </c>
+      <c r="R10" t="n">
+        <v>488.9012013755109</v>
+      </c>
+      <c r="S10" t="n">
+        <v>6.098579226519742</v>
+      </c>
+      <c r="T10" t="n">
+        <v>432.4965</v>
+      </c>
+      <c r="U10" t="n">
+        <v>4.734261848482827</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>-3.6227 ± 0.1151</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>239061.5774 ± 5950.9671</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>488.9012 ± 6.0986</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>432.4965 ± 4.7343</t>
+        </is>
+      </c>
+      <c r="Z10" t="n">
+        <v>4.413004370764007</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>228215.127875</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>384.7859020394597</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>358.1170000000001</v>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SVR_RBF</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.4212895429658632</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>29927.56631504998</v>
+      </c>
+      <c r="E11" t="n">
+        <v>7.275957614183426e-12</v>
+      </c>
+      <c r="F11" t="n">
+        <v>172.9958563522548</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>128.5580091208689</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.842170943040401e-14</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.4213 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>29927.5663 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>172.9959 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>128.5580 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>-2.955492200046144</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>204555.2377474337</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.91038304567337e-11</v>
+      </c>
+      <c r="R11" t="n">
+        <v>452.2778324740599</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5.684341886080801e-14</v>
+      </c>
+      <c r="T11" t="n">
+        <v>391.152038638057</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>-2.9555 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>204555.2377 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>452.2778 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>391.1520 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.376781743012007</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>174627.6714323837</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>279.2819761218051</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>262.5940295171881</v>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AD11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>R2 Mean_TRTR</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>R2 Std_TRTR</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>MSE Mean_TRTR</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>MSE Std_TRTR</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE Mean_TRTR</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE Std_TRTR</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>MAE Mean_TRTR</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>MAE Std_TRTR</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>R2 (Mean±Std)_TRTR</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>MSE (Mean±Std)_TRTR</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE (Mean±Std)_TRTR</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>MAE (Mean±Std)_TRTR</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>R2 Mean_TSTR</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>R2 Std_TSTR</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>MSE Mean_TSTR</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>MSE Std_TSTR</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE Mean_TSTR</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE Std_TSTR</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>MAE Mean_TSTR</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>MAE Std_TSTR</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>R2 (Mean±Std)_TSTR</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>MSE (Mean±Std)_TSTR</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE (Mean±Std)_TSTR</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>MAE (Mean±Std)_TSTR</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>R2_Drop</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>MSE_Increase</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_Increase</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>MAE_Increase</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Synthetic_Model</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ExtraTrees</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.9116048161286496</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.001626983670777651</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4571.288966849999</v>
+      </c>
+      <c r="E2" t="n">
+        <v>84.13820954652159</v>
+      </c>
+      <c r="F2" t="n">
+        <v>67.6084497138725</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6216865261302376</v>
+      </c>
+      <c r="H2" t="n">
+        <v>48.363375</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.4247965326188557</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.9116 ± 0.0016</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>4571.2890 ± 84.1382</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>67.6084 ± 0.6217</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>48.3634 ± 0.4248</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>0.89821192622542</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.001582865470200173</v>
+      </c>
+      <c r="P2" t="n">
+        <v>5263.89197040249</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>81.85667072614146</v>
+      </c>
+      <c r="R2" t="n">
+        <v>72.55047789703573</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.5657979446930377</v>
+      </c>
+      <c r="T2" t="n">
+        <v>50.74721524417826</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.4678670643564188</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.8982 ± 0.0016</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>5263.8920 ± 81.8567</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>72.5505 ± 0.5658</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>50.7472 ± 0.4679</t>
+        </is>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.01339288990322962</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>692.6030035524909</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>4.942028183163231</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.383840244178266</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GradientBoost</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.9102206965008903</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.0001952188595595897</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4642.867649149999</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10.0955932183435</v>
+      </c>
+      <c r="F3" t="n">
+        <v>68.13855121779409</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.0740748948746275</v>
+      </c>
+      <c r="H3" t="n">
+        <v>50.13660360458156</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.09856557051916351</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.9102 ± 0.0002</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>4642.8676 ± 10.0956</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>68.1386 ± 0.0741</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>50.1366 ± 0.0986</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>0.894287995454272</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0005158962547889247</v>
+      </c>
+      <c r="P3" t="n">
+        <v>5466.815033122024</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>26.67917814377794</v>
+      </c>
+      <c r="R3" t="n">
+        <v>73.93769329352111</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.1803983237960215</v>
+      </c>
+      <c r="T3" t="n">
+        <v>54.50148323439273</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.09540391407044091</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.8943 ± 0.0005</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>5466.8150 ± 26.6792</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>73.9377 ± 0.1804</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>54.5015 ± 0.0954</t>
+        </is>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.01593270104661837</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>823.9473839720249</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>5.799142075727019</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>4.364879629811171</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.9028473645236117</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.002042436733120966</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5024.173843</v>
+      </c>
+      <c r="E4" t="n">
+        <v>105.6230452237469</v>
+      </c>
+      <c r="F4" t="n">
+        <v>70.87748756684246</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7453852776203633</v>
+      </c>
+      <c r="H4" t="n">
+        <v>51.09162</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.5291182723172551</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.9028 ± 0.0020</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>5024.1738 ± 105.6230</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>70.8775 ± 0.7454</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>51.0916 ± 0.5291</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>0.8823003623947725</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.001302777485086991</v>
+      </c>
+      <c r="P4" t="n">
+        <v>6086.74625950299</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>67.37213593566581</v>
+      </c>
+      <c r="R4" t="n">
+        <v>78.01641305592763</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.4307590856563655</v>
+      </c>
+      <c r="T4" t="n">
+        <v>56.02874781604841</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.4865870021313796</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0.8823 ± 0.0013</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>6086.7463 ± 67.3721</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>78.0164 ± 0.4308</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>56.0287 ± 0.4866</t>
+        </is>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.0205470021288392</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1062.572416502991</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>7.138925489085167</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>4.93712781604841</v>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>LinearRegression</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.8851906599789372</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1.110223024625157e-16</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5937.276742287724</v>
+      </c>
+      <c r="E5" t="n">
+        <v>9.094947017729282e-13</v>
+      </c>
+      <c r="F5" t="n">
+        <v>77.05372633615926</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.4210854715202e-14</v>
+      </c>
+      <c r="H5" t="n">
+        <v>59.38520770130062</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.8852 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>5937.2767 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>77.0537 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>59.3852 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>0.8818487549702191</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.110223024625157e-16</v>
+      </c>
+      <c r="P5" t="n">
+        <v>6110.100790222825</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>78.1671336958368</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>60.23197618819668</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0.8818 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>6110.1008 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>78.1671 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>60.2320 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.003341905008718116</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>172.8240479351007</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.113407359677538</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.8467684868960603</v>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.8851906081365704</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1.110223024625157e-16</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5937.279423275867</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>77.05374373303265</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>59.38491809936655</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.8852 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>5937.2794 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>77.0537 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>59.3849 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>0.8818467641738094</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>6110.203742728424</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>78.16779223394009</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>60.23250937783867</v>
+      </c>
+      <c r="U6" t="n">
+        <v>7.105427357601002e-15</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0.8818 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>6110.2037 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>78.1678 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>60.2325 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.003343843962760995</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>172.924319452557</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.114048500907444</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.8475912784721231</v>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.8851866436459515</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5937.484443859918</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>77.05507409548002</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>59.37304037963372</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.8852 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>5937.4844 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>77.0551 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>59.3730 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>0.8818062107819195</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>6112.300930208509</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>9.094947017729282e-13</v>
+      </c>
+      <c r="R7" t="n">
+        <v>78.18120573519259</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.4210854715202e-14</v>
+      </c>
+      <c r="T7" t="n">
+        <v>60.24269405476095</v>
+      </c>
+      <c r="U7" t="n">
+        <v>7.105427357601002e-15</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0.8818 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>6112.3009 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>78.1812 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>60.2427 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.003380432864032001</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>174.8164863485918</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.126131639712568</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.8696536751272319</v>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.8851727350548286</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5938.203715955524</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>77.05974121391482</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.4210854715202e-14</v>
+      </c>
+      <c r="H8" t="n">
+        <v>59.35659563760858</v>
+      </c>
+      <c r="I8" t="n">
+        <v>7.105427357601002e-15</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.8852 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>5938.2037 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>77.0597 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>59.3566 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>0.8817659835899285</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>6114.38124851163</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>9.094947017729282e-13</v>
+      </c>
+      <c r="R8" t="n">
+        <v>78.1945090688063</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>60.25220599310809</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0.8818 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>6114.3812 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>78.1945 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>60.2522 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.003406751464900104</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>176.1775325561066</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.134767854891479</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.8956103554995138</v>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.8823432762978853</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.110223024625157e-16</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6084.527</v>
+      </c>
+      <c r="E9" t="n">
+        <v>9.094947017729282e-13</v>
+      </c>
+      <c r="F9" t="n">
+        <v>78.00337813197578</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.4210854715202e-14</v>
+      </c>
+      <c r="H9" t="n">
+        <v>54.43299999999999</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.8823 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>6084.5270 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>78.0034 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>54.4330 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>0.8783794804989883</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>6289.511651977378</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>79.30644142802889</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.4210854715202e-14</v>
+      </c>
+      <c r="T9" t="n">
+        <v>57.13860957816318</v>
+      </c>
+      <c r="U9" t="n">
+        <v>7.105427357601002e-15</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0.8784 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>6289.5117 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>79.3064 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>57.1386 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.003963795798897052</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>204.9846519773782</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.303063296053111</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.705609578163184</v>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.790261804743337</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.01019794917541283</v>
+      </c>
+      <c r="D10" t="n">
+        <v>10846.4495</v>
+      </c>
+      <c r="E10" t="n">
+        <v>527.3791004033532</v>
+      </c>
+      <c r="F10" t="n">
+        <v>104.1152993360513</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.54046140778499</v>
+      </c>
+      <c r="H10" t="n">
+        <v>74.37949999999998</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.635971347548608</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.7903 ± 0.0102</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>10846.4495 ± 527.3791</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>104.1153 ± 2.5405</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>74.3795 ± 1.6360</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>0.8141560514760513</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.008297002815105507</v>
+      </c>
+      <c r="P10" t="n">
+        <v>9610.776902503985</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>429.0731210177173</v>
+      </c>
+      <c r="R10" t="n">
+        <v>98.01060867110824</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.167369470779278</v>
+      </c>
+      <c r="T10" t="n">
+        <v>70.89553017204551</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.8758232940337414</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0.8142 ± 0.0083</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>9610.7769 ± 429.0731</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>98.0106 ± 2.1674</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>70.8955 ± 0.8758</t>
+        </is>
+      </c>
+      <c r="Z10" t="n">
+        <v>-0.02389424673271434</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-1235.672597496014</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-6.104690664943007</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-3.483969827954468</v>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SVR_RBF</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.4212895429658632</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>29927.56631504998</v>
+      </c>
+      <c r="E11" t="n">
+        <v>7.275957614183426e-12</v>
+      </c>
+      <c r="F11" t="n">
+        <v>172.9958563522548</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>128.5580091208689</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.842170943040401e-14</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.4213 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>29927.5663 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>172.9959 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>128.5580 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>0.5206722866263351</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>24788.06414204027</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>157.4422565324833</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>115.1602725845352</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.4210854715202e-14</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0.5207 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>24788.0641 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>157.4423 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>115.1603 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Z11" t="n">
+        <v>-0.09938274366047195</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-5139.502173009711</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-15.55359981977153</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-13.39773653633364</v>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
         </is>
       </c>
     </row>
@@ -1798,67 +4370,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>R2 Mean</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>R2 Std</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>MSE Mean</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>MSE Std</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>RMSE Mean</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RMSE Std</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>MAE Mean</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MAE Std</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>R2 (Mean±Std)</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>MSE (Mean±Std)</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>RMSE (Mean±Std)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>MAE (Mean±Std)</t>
         </is>
@@ -2385,156 +4957,156 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD61"/>
+  <dimension ref="A1:AD81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>R2 Mean_TRTR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>R2 Std_TRTR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>MSE Mean_TRTR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>MSE Std_TRTR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>RMSE Mean_TRTR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RMSE Std_TRTR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>MAE Mean_TRTR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MAE Std_TRTR</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>R2 (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>MSE (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>RMSE (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>MAE (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>R2 Mean_TSTR</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>R2 Std_TSTR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>MSE Mean_TSTR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>MSE Std_TSTR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>RMSE Mean_TSTR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>RMSE Std_TSTR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>MAE Mean_TSTR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>MAE Std_TSTR</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>R2 (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>MSE (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>RMSE (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>MAE (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>R2_Drop</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>MSE_Increase</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>RMSE_Increase</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>MAE_Increase</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
@@ -9257,6 +11829,2246 @@
       <c r="AD61" t="inlineStr">
         <is>
           <t>GaussianCopula</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ExtraTrees</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>0.9116048161286496</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.001626983670777651</v>
+      </c>
+      <c r="D62" t="n">
+        <v>4571.288966849999</v>
+      </c>
+      <c r="E62" t="n">
+        <v>84.13820954652159</v>
+      </c>
+      <c r="F62" t="n">
+        <v>67.6084497138725</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.6216865261302376</v>
+      </c>
+      <c r="H62" t="n">
+        <v>48.363375</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.4247965326188557</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>0.9116 ± 0.0016</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>4571.2890 ± 84.1382</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>67.6084 ± 0.6217</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>48.3634 ± 0.4248</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>-0.2476985211651928</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0.1063491796695852</v>
+      </c>
+      <c r="P62" t="n">
+        <v>64523.76966666502</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>5499.766054728349</v>
+      </c>
+      <c r="R62" t="n">
+        <v>253.772829810411</v>
+      </c>
+      <c r="S62" t="n">
+        <v>11.09596848775243</v>
+      </c>
+      <c r="T62" t="n">
+        <v>200.6349508907648</v>
+      </c>
+      <c r="U62" t="n">
+        <v>11.36178203789082</v>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>-0.2477 ± 0.1063</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>64523.7697 ± 5499.7661</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>253.7728 ± 11.0960</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>200.6350 ± 11.3618</t>
+        </is>
+      </c>
+      <c r="Z62" t="n">
+        <v>1.159303337293842</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>59952.48069981502</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>186.1643800965385</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>152.2715758907648</v>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>GradientBoost</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>0.9102206965008903</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.0001952188595595897</v>
+      </c>
+      <c r="D63" t="n">
+        <v>4642.867649149999</v>
+      </c>
+      <c r="E63" t="n">
+        <v>10.0955932183435</v>
+      </c>
+      <c r="F63" t="n">
+        <v>68.13855121779409</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.0740748948746275</v>
+      </c>
+      <c r="H63" t="n">
+        <v>50.13660360458156</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.09856557051916351</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>0.9102 ± 0.0002</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>4642.8676 ± 10.0956</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>68.1386 ± 0.0741</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>50.1366 ± 0.0986</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>0.1580785346976827</v>
+      </c>
+      <c r="O63" t="n">
+        <v>3.657001166779273e-16</v>
+      </c>
+      <c r="P63" t="n">
+        <v>43539.32122469468</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>1.9387389466973e-11</v>
+      </c>
+      <c r="R63" t="n">
+        <v>208.6607802743359</v>
+      </c>
+      <c r="S63" t="n">
+        <v>4.403072291788041e-14</v>
+      </c>
+      <c r="T63" t="n">
+        <v>162.3152754450487</v>
+      </c>
+      <c r="U63" t="n">
+        <v>4.493866839778178e-14</v>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>0.1581 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>43539.3212 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>208.6608 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>162.3153 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Z63" t="n">
+        <v>0.7521421618032076</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>38896.45357554468</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>140.5222290565418</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>112.1786718404672</v>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>0.9028473645236117</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.002042436733120966</v>
+      </c>
+      <c r="D64" t="n">
+        <v>5024.173843</v>
+      </c>
+      <c r="E64" t="n">
+        <v>105.6230452237469</v>
+      </c>
+      <c r="F64" t="n">
+        <v>70.87748756684246</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.7453852776203633</v>
+      </c>
+      <c r="H64" t="n">
+        <v>51.09162</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.5291182723172551</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>0.9028 ± 0.0020</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>5024.1738 ± 105.6230</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>70.8775 ± 0.7454</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>51.0916 ± 0.5291</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>-0.2937394689168336</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0.06936555461018579</v>
+      </c>
+      <c r="P64" t="n">
+        <v>66904.74187875641</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>3587.186321490817</v>
+      </c>
+      <c r="R64" t="n">
+        <v>258.5645689784054</v>
+      </c>
+      <c r="S64" t="n">
+        <v>7.007535070753652</v>
+      </c>
+      <c r="T64" t="n">
+        <v>194.6835479481866</v>
+      </c>
+      <c r="U64" t="n">
+        <v>7.007873836343863</v>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>-0.2937 ± 0.0694</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>66904.7419 ± 3587.1863</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>258.5646 ± 7.0075</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>194.6835 ± 7.0079</t>
+        </is>
+      </c>
+      <c r="Z64" t="n">
+        <v>1.196586833440445</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>61880.56803575641</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>187.687081411563</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>143.5919279481866</v>
+      </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>LinearRegression</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>0.8851906599789372</v>
+      </c>
+      <c r="C65" t="n">
+        <v>1.110223024625157e-16</v>
+      </c>
+      <c r="D65" t="n">
+        <v>5937.276742287724</v>
+      </c>
+      <c r="E65" t="n">
+        <v>9.094947017729282e-13</v>
+      </c>
+      <c r="F65" t="n">
+        <v>77.05372633615926</v>
+      </c>
+      <c r="G65" t="n">
+        <v>1.4210854715202e-14</v>
+      </c>
+      <c r="H65" t="n">
+        <v>59.38520770130062</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>0.8852 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>5937.2767 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>77.0537 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>59.3852 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>-0.1550190367355349</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>59730.92139064085</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>7.275957614183426e-12</v>
+      </c>
+      <c r="R65" t="n">
+        <v>244.3991026796965</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>193.990499676167</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>-0.1550 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>59730.9214 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>244.3991 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>193.9905 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Z65" t="n">
+        <v>1.040209696714472</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>53793.64464835313</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>167.3453763435373</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>134.6052919748664</v>
+      </c>
+      <c r="AD65" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>0.8851906081365704</v>
+      </c>
+      <c r="C66" t="n">
+        <v>1.110223024625157e-16</v>
+      </c>
+      <c r="D66" t="n">
+        <v>5937.279423275867</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>77.05374373303265</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>59.38491809936655</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>0.8852 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>5937.2794 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>77.0537 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>59.3849 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>-0.1550127975995497</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="n">
+        <v>59730.59873852064</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>244.3984425861193</v>
+      </c>
+      <c r="S66" t="n">
+        <v>2.842170943040401e-14</v>
+      </c>
+      <c r="T66" t="n">
+        <v>193.9900329807481</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>-0.1550 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>59730.5987 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>244.3984 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>193.9900 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Z66" t="n">
+        <v>1.04020340573612</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>53793.31931524477</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>167.3446988530866</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>134.6051148813815</v>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>0.8851866436459515</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" t="n">
+        <v>5937.484443859918</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="n">
+        <v>77.05507409548002</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>59.37304037963372</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>0.8852 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>5937.4844 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>77.0551 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>59.3730 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>-0.1546172572629998</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
+        <v>59710.14367414693</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>7.275957614183426e-12</v>
+      </c>
+      <c r="R67" t="n">
+        <v>244.3565912230462</v>
+      </c>
+      <c r="S67" t="n">
+        <v>2.842170943040401e-14</v>
+      </c>
+      <c r="T67" t="n">
+        <v>193.9600260389704</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>-0.1546 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>59710.1437 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>244.3566 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>193.9600 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Z67" t="n">
+        <v>1.039803900908951</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>53772.65923028701</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>167.3015171275662</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>134.5869856593367</v>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>0.8851727350548286</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" t="n">
+        <v>5938.203715955524</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
+        <v>77.05974121391482</v>
+      </c>
+      <c r="G68" t="n">
+        <v>1.4210854715202e-14</v>
+      </c>
+      <c r="H68" t="n">
+        <v>59.35659563760858</v>
+      </c>
+      <c r="I68" t="n">
+        <v>7.105427357601002e-15</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>0.8852 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>5938.2037 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>77.0597 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>59.3566 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>-0.1542229437520715</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="n">
+        <v>59689.75205411694</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>7.275957614183426e-12</v>
+      </c>
+      <c r="R68" t="n">
+        <v>244.3148625321778</v>
+      </c>
+      <c r="S68" t="n">
+        <v>2.842170943040401e-14</v>
+      </c>
+      <c r="T68" t="n">
+        <v>193.9300943300856</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>-0.1542 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>59689.7521 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>244.3149 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>193.9301 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Z68" t="n">
+        <v>1.0393956788069</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>53751.54833816141</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>167.2551213182629</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>134.5734986924771</v>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>0.8823432762978853</v>
+      </c>
+      <c r="C69" t="n">
+        <v>1.110223024625157e-16</v>
+      </c>
+      <c r="D69" t="n">
+        <v>6084.527</v>
+      </c>
+      <c r="E69" t="n">
+        <v>9.094947017729282e-13</v>
+      </c>
+      <c r="F69" t="n">
+        <v>78.00337813197578</v>
+      </c>
+      <c r="G69" t="n">
+        <v>1.4210854715202e-14</v>
+      </c>
+      <c r="H69" t="n">
+        <v>54.43299999999999</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>0.8823 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>6084.5270 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>78.0034 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>54.4330 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>-5.168602711759162</v>
+      </c>
+      <c r="O69" t="n">
+        <v>8.881784197001252e-16</v>
+      </c>
+      <c r="P69" t="n">
+        <v>319004.5461999999</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>5.820766091346741e-11</v>
+      </c>
+      <c r="R69" t="n">
+        <v>564.8048744478041</v>
+      </c>
+      <c r="S69" t="n">
+        <v>1.13686837721616e-13</v>
+      </c>
+      <c r="T69" t="n">
+        <v>492.295</v>
+      </c>
+      <c r="U69" t="n">
+        <v>5.684341886080801e-14</v>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>-5.1686 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>319004.5462 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>564.8049 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>492.2950 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Z69" t="n">
+        <v>6.050945988057047</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>312920.0191999999</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>486.8014963158283</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>437.862</v>
+      </c>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>0.790261804743337</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0.01019794917541283</v>
+      </c>
+      <c r="D70" t="n">
+        <v>10846.4495</v>
+      </c>
+      <c r="E70" t="n">
+        <v>527.3791004033532</v>
+      </c>
+      <c r="F70" t="n">
+        <v>104.1152993360513</v>
+      </c>
+      <c r="G70" t="n">
+        <v>2.54046140778499</v>
+      </c>
+      <c r="H70" t="n">
+        <v>74.37949999999998</v>
+      </c>
+      <c r="I70" t="n">
+        <v>1.635971347548608</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>0.7903 ± 0.0102</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>10846.4495 ± 527.3791</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>104.1153 ± 2.5405</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>74.3795 ± 1.6360</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>-3.62274256602067</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0.1150740718166244</v>
+      </c>
+      <c r="P70" t="n">
+        <v>239061.577375</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>5950.967143542908</v>
+      </c>
+      <c r="R70" t="n">
+        <v>488.9012013755109</v>
+      </c>
+      <c r="S70" t="n">
+        <v>6.098579226519742</v>
+      </c>
+      <c r="T70" t="n">
+        <v>432.4965</v>
+      </c>
+      <c r="U70" t="n">
+        <v>4.734261848482827</v>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>-3.6227 ± 0.1151</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>239061.5774 ± 5950.9671</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>488.9012 ± 6.0986</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>432.4965 ± 4.7343</t>
+        </is>
+      </c>
+      <c r="Z70" t="n">
+        <v>4.413004370764007</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>228215.127875</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>384.7859020394597</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>358.1170000000001</v>
+      </c>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>SVR_RBF</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>0.4212895429658632</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" t="n">
+        <v>29927.56631504998</v>
+      </c>
+      <c r="E71" t="n">
+        <v>7.275957614183426e-12</v>
+      </c>
+      <c r="F71" t="n">
+        <v>172.9958563522548</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>128.5580091208689</v>
+      </c>
+      <c r="I71" t="n">
+        <v>2.842170943040401e-14</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>0.4213 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>29927.5663 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>172.9959 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>128.5580 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>-2.955492200046144</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>204555.2377474337</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>2.91038304567337e-11</v>
+      </c>
+      <c r="R71" t="n">
+        <v>452.2778324740599</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5.684341886080801e-14</v>
+      </c>
+      <c r="T71" t="n">
+        <v>391.152038638057</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>-2.9555 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>204555.2377 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>452.2778 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>391.1520 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Z71" t="n">
+        <v>3.376781743012007</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>174627.6714323837</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>279.2819761218051</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>262.5940295171881</v>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ExtraTrees</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>0.9116048161286496</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0.001626983670777651</v>
+      </c>
+      <c r="D72" t="n">
+        <v>4571.288966849999</v>
+      </c>
+      <c r="E72" t="n">
+        <v>84.13820954652159</v>
+      </c>
+      <c r="F72" t="n">
+        <v>67.6084497138725</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.6216865261302376</v>
+      </c>
+      <c r="H72" t="n">
+        <v>48.363375</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.4247965326188557</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>0.9116 ± 0.0016</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>4571.2890 ± 84.1382</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>67.6084 ± 0.6217</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>48.3634 ± 0.4248</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>0.89821192622542</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0.001582865470200173</v>
+      </c>
+      <c r="P72" t="n">
+        <v>5263.89197040249</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>81.85667072614146</v>
+      </c>
+      <c r="R72" t="n">
+        <v>72.55047789703573</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0.5657979446930377</v>
+      </c>
+      <c r="T72" t="n">
+        <v>50.74721524417826</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0.4678670643564188</v>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>0.8982 ± 0.0016</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>5263.8920 ± 81.8567</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>72.5505 ± 0.5658</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>50.7472 ± 0.4679</t>
+        </is>
+      </c>
+      <c r="Z72" t="n">
+        <v>0.01339288990322962</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>692.6030035524909</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>4.942028183163231</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>2.383840244178266</v>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>GradientBoost</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>0.9102206965008903</v>
+      </c>
+      <c r="C73" t="n">
+        <v>0.0001952188595595897</v>
+      </c>
+      <c r="D73" t="n">
+        <v>4642.867649149999</v>
+      </c>
+      <c r="E73" t="n">
+        <v>10.0955932183435</v>
+      </c>
+      <c r="F73" t="n">
+        <v>68.13855121779409</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.0740748948746275</v>
+      </c>
+      <c r="H73" t="n">
+        <v>50.13660360458156</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.09856557051916351</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>0.9102 ± 0.0002</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>4642.8676 ± 10.0956</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>68.1386 ± 0.0741</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>50.1366 ± 0.0986</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>0.894287995454272</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0.0005158962547889247</v>
+      </c>
+      <c r="P73" t="n">
+        <v>5466.815033122024</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>26.67917814377794</v>
+      </c>
+      <c r="R73" t="n">
+        <v>73.93769329352111</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0.1803983237960215</v>
+      </c>
+      <c r="T73" t="n">
+        <v>54.50148323439273</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0.09540391407044091</v>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>0.8943 ± 0.0005</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>5466.8150 ± 26.6792</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>73.9377 ± 0.1804</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>54.5015 ± 0.0954</t>
+        </is>
+      </c>
+      <c r="Z73" t="n">
+        <v>0.01593270104661837</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>823.9473839720249</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>5.799142075727019</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>4.364879629811171</v>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>0.9028473645236117</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0.002042436733120966</v>
+      </c>
+      <c r="D74" t="n">
+        <v>5024.173843</v>
+      </c>
+      <c r="E74" t="n">
+        <v>105.6230452237469</v>
+      </c>
+      <c r="F74" t="n">
+        <v>70.87748756684246</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.7453852776203633</v>
+      </c>
+      <c r="H74" t="n">
+        <v>51.09162</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.5291182723172551</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>0.9028 ± 0.0020</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>5024.1738 ± 105.6230</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>70.8775 ± 0.7454</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>51.0916 ± 0.5291</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>0.8823003623947725</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0.001302777485086991</v>
+      </c>
+      <c r="P74" t="n">
+        <v>6086.74625950299</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>67.37213593566581</v>
+      </c>
+      <c r="R74" t="n">
+        <v>78.01641305592763</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0.4307590856563655</v>
+      </c>
+      <c r="T74" t="n">
+        <v>56.02874781604841</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0.4865870021313796</v>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>0.8823 ± 0.0013</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>6086.7463 ± 67.3721</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>78.0164 ± 0.4308</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>56.0287 ± 0.4866</t>
+        </is>
+      </c>
+      <c r="Z74" t="n">
+        <v>0.0205470021288392</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>1062.572416502991</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>7.138925489085167</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>4.93712781604841</v>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>LinearRegression</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>0.8851906599789372</v>
+      </c>
+      <c r="C75" t="n">
+        <v>1.110223024625157e-16</v>
+      </c>
+      <c r="D75" t="n">
+        <v>5937.276742287724</v>
+      </c>
+      <c r="E75" t="n">
+        <v>9.094947017729282e-13</v>
+      </c>
+      <c r="F75" t="n">
+        <v>77.05372633615926</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1.4210854715202e-14</v>
+      </c>
+      <c r="H75" t="n">
+        <v>59.38520770130062</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>0.8852 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>5937.2767 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>77.0537 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>59.3852 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>0.8818487549702191</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1.110223024625157e-16</v>
+      </c>
+      <c r="P75" t="n">
+        <v>6110.100790222825</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>78.1671336958368</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>60.23197618819668</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>0.8818 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>6110.1008 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>78.1671 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>60.2320 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.003341905008718116</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>172.8240479351007</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.113407359677538</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.8467684868960603</v>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>0.8851906081365704</v>
+      </c>
+      <c r="C76" t="n">
+        <v>1.110223024625157e-16</v>
+      </c>
+      <c r="D76" t="n">
+        <v>5937.279423275867</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" t="n">
+        <v>77.05374373303265</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>59.38491809936655</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>0.8852 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>5937.2794 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>77.0537 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>59.3849 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>0.8818467641738094</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>6110.203742728424</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" t="n">
+        <v>78.16779223394009</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>60.23250937783867</v>
+      </c>
+      <c r="U76" t="n">
+        <v>7.105427357601002e-15</v>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>0.8818 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>6110.2037 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>78.1678 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>60.2325 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Z76" t="n">
+        <v>0.003343843962760995</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>172.924319452557</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>1.114048500907444</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>0.8475912784721231</v>
+      </c>
+      <c r="AD76" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>0.8851866436459515</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" t="n">
+        <v>5937.484443859918</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="n">
+        <v>77.05507409548002</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>59.37304037963372</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>0.8852 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>5937.4844 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>77.0551 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>59.3730 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>0.8818062107819195</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>6112.300930208509</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>9.094947017729282e-13</v>
+      </c>
+      <c r="R77" t="n">
+        <v>78.18120573519259</v>
+      </c>
+      <c r="S77" t="n">
+        <v>1.4210854715202e-14</v>
+      </c>
+      <c r="T77" t="n">
+        <v>60.24269405476095</v>
+      </c>
+      <c r="U77" t="n">
+        <v>7.105427357601002e-15</v>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>0.8818 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>6112.3009 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>78.1812 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>60.2427 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Z77" t="n">
+        <v>0.003380432864032001</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>174.8164863485918</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>1.126131639712568</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>0.8696536751272319</v>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>0.8851727350548286</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" t="n">
+        <v>5938.203715955524</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" t="n">
+        <v>77.05974121391482</v>
+      </c>
+      <c r="G78" t="n">
+        <v>1.4210854715202e-14</v>
+      </c>
+      <c r="H78" t="n">
+        <v>59.35659563760858</v>
+      </c>
+      <c r="I78" t="n">
+        <v>7.105427357601002e-15</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>0.8852 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>5938.2037 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>77.0597 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>59.3566 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>0.8817659835899285</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>6114.38124851163</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>9.094947017729282e-13</v>
+      </c>
+      <c r="R78" t="n">
+        <v>78.1945090688063</v>
+      </c>
+      <c r="S78" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>60.25220599310809</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0</v>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>0.8818 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>6114.3812 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>78.1945 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>60.2522 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Z78" t="n">
+        <v>0.003406751464900104</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>176.1775325561066</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>1.134767854891479</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>0.8956103554995138</v>
+      </c>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>0.8823432762978853</v>
+      </c>
+      <c r="C79" t="n">
+        <v>1.110223024625157e-16</v>
+      </c>
+      <c r="D79" t="n">
+        <v>6084.527</v>
+      </c>
+      <c r="E79" t="n">
+        <v>9.094947017729282e-13</v>
+      </c>
+      <c r="F79" t="n">
+        <v>78.00337813197578</v>
+      </c>
+      <c r="G79" t="n">
+        <v>1.4210854715202e-14</v>
+      </c>
+      <c r="H79" t="n">
+        <v>54.43299999999999</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>0.8823 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>6084.5270 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>78.0034 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>54.4330 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>0.8783794804989883</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>6289.511651977378</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" t="n">
+        <v>79.30644142802889</v>
+      </c>
+      <c r="S79" t="n">
+        <v>1.4210854715202e-14</v>
+      </c>
+      <c r="T79" t="n">
+        <v>57.13860957816318</v>
+      </c>
+      <c r="U79" t="n">
+        <v>7.105427357601002e-15</v>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>0.8784 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>6289.5117 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>79.3064 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>57.1386 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Z79" t="n">
+        <v>0.003963795798897052</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>204.9846519773782</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>1.303063296053111</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>2.705609578163184</v>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>0.790261804743337</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0.01019794917541283</v>
+      </c>
+      <c r="D80" t="n">
+        <v>10846.4495</v>
+      </c>
+      <c r="E80" t="n">
+        <v>527.3791004033532</v>
+      </c>
+      <c r="F80" t="n">
+        <v>104.1152993360513</v>
+      </c>
+      <c r="G80" t="n">
+        <v>2.54046140778499</v>
+      </c>
+      <c r="H80" t="n">
+        <v>74.37949999999998</v>
+      </c>
+      <c r="I80" t="n">
+        <v>1.635971347548608</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>0.7903 ± 0.0102</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>10846.4495 ± 527.3791</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>104.1153 ± 2.5405</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>74.3795 ± 1.6360</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>0.8141560514760513</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0.008297002815105507</v>
+      </c>
+      <c r="P80" t="n">
+        <v>9610.776902503985</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>429.0731210177173</v>
+      </c>
+      <c r="R80" t="n">
+        <v>98.01060867110824</v>
+      </c>
+      <c r="S80" t="n">
+        <v>2.167369470779278</v>
+      </c>
+      <c r="T80" t="n">
+        <v>70.89553017204551</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0.8758232940337414</v>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>0.8142 ± 0.0083</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>9610.7769 ± 429.0731</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>98.0106 ± 2.1674</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>70.8955 ± 0.8758</t>
+        </is>
+      </c>
+      <c r="Z80" t="n">
+        <v>-0.02389424673271434</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>-1235.672597496014</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>-6.104690664943007</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>-3.483969827954468</v>
+      </c>
+      <c r="AD80" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>SVR_RBF</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>0.4212895429658632</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" t="n">
+        <v>29927.56631504998</v>
+      </c>
+      <c r="E81" t="n">
+        <v>7.275957614183426e-12</v>
+      </c>
+      <c r="F81" t="n">
+        <v>172.9958563522548</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>128.5580091208689</v>
+      </c>
+      <c r="I81" t="n">
+        <v>2.842170943040401e-14</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>0.4213 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>29927.5663 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>172.9959 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>128.5580 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>0.5206722866263351</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>24788.06414204027</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" t="n">
+        <v>157.4422565324833</v>
+      </c>
+      <c r="S81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" t="n">
+        <v>115.1602725845352</v>
+      </c>
+      <c r="U81" t="n">
+        <v>1.4210854715202e-14</v>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>0.5207 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>24788.0641 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>157.4423 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>115.1603 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Z81" t="n">
+        <v>-0.09938274366047195</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>-5139.502173009711</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>-15.55359981977153</v>
+      </c>
+      <c r="AC81" t="n">
+        <v>-13.39773653633364</v>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
         </is>
       </c>
     </row>
@@ -9271,31 +14083,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>R2_Drop</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>MSE_Increase</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>RMSE_Increase</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>MAE_Increase</t>
         </is>
@@ -9413,6 +14225,44 @@
       </c>
       <c r="E7" t="n">
         <v>0.4694465391804445</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>-0.005596766821519083</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-289.4324928208483</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.2013223914503016</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.09693746999078527</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.1108377116537</v>
+      </c>
+      <c r="C9" t="n">
+        <v>109160.3492350546</v>
+      </c>
+      <c r="D9" t="n">
+        <v>233.4489778684189</v>
+      </c>
+      <c r="E9" t="n">
+        <v>200.4986096404668</v>
       </c>
     </row>
   </sheetData>
@@ -9430,152 +14280,152 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>R2 Mean_TRTR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>R2 Std_TRTR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>MSE Mean_TRTR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>MSE Std_TRTR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>RMSE Mean_TRTR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RMSE Std_TRTR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>MAE Mean_TRTR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MAE Std_TRTR</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>R2 (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>MSE (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>RMSE (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>MAE (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>R2 Mean_TSTR</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>R2 Std_TSTR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>MSE Mean_TSTR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>MSE Std_TSTR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>RMSE Mean_TSTR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>RMSE Std_TSTR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>MAE Mean_TSTR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>MAE Std_TSTR</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>R2 (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>MSE (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>RMSE (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>MAE (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>R2_Drop</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>MSE_Increase</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>RMSE_Increase</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>MAE_Increase</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
@@ -10716,152 +15566,152 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>R2 Mean_TRTR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>R2 Std_TRTR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>MSE Mean_TRTR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>MSE Std_TRTR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>RMSE Mean_TRTR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RMSE Std_TRTR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>MAE Mean_TRTR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MAE Std_TRTR</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>R2 (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>MSE (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>RMSE (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>MAE (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>R2 Mean_TSTR</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>R2 Std_TSTR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>MSE Mean_TSTR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>MSE Std_TSTR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>RMSE Mean_TSTR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>RMSE Std_TSTR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>MAE Mean_TSTR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>MAE Std_TSTR</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>R2 (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>MSE (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>RMSE (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>MAE (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>R2_Drop</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>MSE_Increase</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>RMSE_Increase</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>MAE_Increase</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
@@ -12002,152 +16852,152 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>R2 Mean_TRTR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>R2 Std_TRTR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>MSE Mean_TRTR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>MSE Std_TRTR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>RMSE Mean_TRTR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RMSE Std_TRTR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>MAE Mean_TRTR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MAE Std_TRTR</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>R2 (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>MSE (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>RMSE (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>MAE (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>R2 Mean_TSTR</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>R2 Std_TSTR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>MSE Mean_TSTR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>MSE Std_TSTR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>RMSE Mean_TSTR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>RMSE Std_TSTR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>MAE Mean_TSTR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>MAE Std_TSTR</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>R2 (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>MSE (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>RMSE (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>MAE (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>R2_Drop</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>MSE_Increase</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>RMSE_Increase</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>MAE_Increase</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
@@ -13288,152 +18138,152 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>R2 Mean_TRTR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>R2 Std_TRTR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>MSE Mean_TRTR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>MSE Std_TRTR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>RMSE Mean_TRTR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RMSE Std_TRTR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>MAE Mean_TRTR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MAE Std_TRTR</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>R2 (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>MSE (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>RMSE (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>MAE (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>R2 Mean_TSTR</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>R2 Std_TSTR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>MSE Mean_TSTR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>MSE Std_TSTR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>RMSE Mean_TSTR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>RMSE Std_TSTR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>MAE Mean_TSTR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>MAE Std_TSTR</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>R2 (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>MSE (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>RMSE (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>MAE (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>R2_Drop</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>MSE_Increase</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>RMSE_Increase</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>MAE_Increase</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
@@ -14574,152 +19424,152 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>R2 Mean_TRTR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>R2 Std_TRTR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>MSE Mean_TRTR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>MSE Std_TRTR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>RMSE Mean_TRTR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RMSE Std_TRTR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>MAE Mean_TRTR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MAE Std_TRTR</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>R2 (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>MSE (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>RMSE (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>MAE (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>R2 Mean_TSTR</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>R2 Std_TSTR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>MSE Mean_TSTR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>MSE Std_TSTR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>RMSE Mean_TSTR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>RMSE Std_TSTR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>MAE Mean_TSTR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>MAE Std_TSTR</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>R2 (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>MSE (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>RMSE (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>MAE (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>R2_Drop</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>MSE_Increase</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>RMSE_Increase</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>MAE_Increase</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
